--- a/docs/olife-geo/걸세_세테기_나라도시테마_분류.xlsx
+++ b/docs/olife-geo/걸세_세테기_나라도시테마_분류.xlsx
@@ -388,7 +388,7 @@
     <t>태국;오만;몽골;카자흐스탄;독일;뉴질랜드;에콰도르;아르헨티나</t>
   </si>
   <si>
-    <t>방콕;매끌렁 시장;파타야;니즈와;드레스덴;오클랜드;오타고 반도;산타크루스 섬;부에노스아이레스;마타데로</t>
+    <t>방콕;매끌렁 시장;파타야;니즈와;드레스덴;오클랜드;오타고 반도;산타크루스 섬;부에노스아이레스;마타데로;알마티;몽골 중부 초원</t>
   </si>
   <si>
     <t>사용자 제공(2026-10-27)</t>

--- a/docs/olife-geo/걸세_세테기_나라도시테마_분류.xlsx
+++ b/docs/olife-geo/걸세_세테기_나라도시테마_분류.xlsx
@@ -18073,7 +18073,7 @@
         <v>37</v>
       </c>
       <c r="Z11" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="AA11" t="s">
         <v>41</v>
